--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,6 +618,81 @@
         <v>1</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>16:51:58</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Монетка</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16:52:09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Мария-Ра</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Новосибирск</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:52:18</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Фикс Прайс</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
